--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0096.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0096.xlsx
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Con sâu xanh lục ta vừa thấy... Nó không có trong Hồ sơ Loài vùng Frostlands của Viện...</t>
+          <t>Con sâu xanh lục tao vừa thấy... Nó không có trong Hồ sơ Loài vùng Frostlands của Viện...</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Xong việc ở đây, chúng ta hãy quay về Rừng Bjartr trước nhé.</t>
+          <t>Xong việc ở đây, chúng ta hãy quay về Bjartr Woods trước nhé.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Xong việc ở đây, chúng ta hãy quay về Rừng Bjartr trước nhé.</t>
+          <t>Xong việc ở đây, chúng ta hãy quay về Bjartr Woods trước nhé.</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Đừng có mà bảo lại nghe từ "người trong cuộc" nào đó nữa. Ta thề nếu ngươi lừa chúng ta—</t>
+          <t>Đừng có mà bảo lại nghe từ "người trong cuộc" nào đó nữa. Tao thề nếu mày lừa chúng tao—</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Ta từng xem mô phỏng tái tạo trong lớp, nhưng những khu rừng ngoài đời chắc phải ngoạn mục và sống động hơn nhiều.</t>
+          <t>Tao từng xem mô phỏng tái tạo trong lớp, nhưng những khu rừng ngoài đời chắc phải ngoạn mục và sống động hơn nhiều.</t>
         </is>
       </c>
     </row>
@@ -14484,7 +14484,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Ugh, ta vừa sửa cái này cách đây không lâu! Tới mức này thì ngay cả loại bê tông tự sửa này cũng sắp bỏ cuộc...</t>
+          <t>Ugh, tao vừa sửa cái này cách đây không lâu! Tới mức này thì ngay cả loại bê tông tự sửa này cũng sắp bỏ cuộc...</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Chào mừng đến Viện Nghiên Cứu, lính mới! Để ta hướng dẫn cậu qua buổi định hướng...</t>
+          <t>Chào mừng đến Viện Nghiên Cứu, lính mới! Để tao hướng dẫn cậu qua buổi định hướng...</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Chào mừng đến Viện Nghiên Cứu, lính mới! Để ta hướng dẫn cậu qua buổi định hướng...</t>
+          <t>Chào mừng đến Viện Nghiên Cứu, lính mới! Để tao hướng dẫn cậu qua buổi định hướng...</t>
         </is>
       </c>
     </row>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>...Vậy thì đi nấu cơm cho ta đi.</t>
+          <t>...Vậy thì đi nấu cơm cho tao đi.</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Ôi trời ơi! Ta chỉ lơ đãng một giây mà ba lô giữ nhiệt mở tung... Giờ mọi thứ đông cứng hết rồi. Kể cả Bright &amp; Brisk Energy Gel của ta...</t>
+          <t>Ôi trời ơi! Tao chỉ lơ đãng một giây mà ba lô giữ nhiệt mở tung... Giờ mọi thứ đông cứng hết rồi. Kể cả Bright &amp; Brisk Energy Gel của tao...</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Ta không phải dân ở đây...</t>
+          <t>Tao không phải dân ở đây...</t>
         </is>
       </c>
     </row>
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>G-Giờ ta phải làm sao? Gọi dừng khẩn cấp à?</t>
+          <t>G-Giờ tao phải làm sao? Gọi dừng khẩn cấp à?</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Năm con tuần lộc máy chắn ngang đường ray rồi. Giờ lại thêm một con nữa ở đường kế bên... T-Ta phải làm gì bây giờ? Gọi dừng khẩn cấp à?</t>
+          <t>Năm con tuần lộc máy chắn ngang đường ray rồi. Giờ lại thêm một con nữa ở đường kế bên... T-Tao phải làm gì bây giờ? Gọi dừng khẩn cấp à?</t>
         </is>
       </c>
     </row>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Tiền bối xem con Clockatoo kia kìa, rõ là đã quá cũ kỹ rồi. Sao người ta không cho nó "nghỉ hưu" nhỉ?</t>
+          <t>bạn xem con Clockatoo kia kìa, rõ là đã quá cũ kỹ rồi. Sao người ta không cho nó "nghỉ hưu" nhỉ?</t>
         </is>
       </c>
     </row>
@@ -24104,7 +24104,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Tiền bối xem con Clockatoo kia kìa, rõ là đã quá cũ kỹ rồi. Sao người ta không cho nó "nghỉ hưu" nhỉ?</t>
+          <t>bạn xem con Clockatoo kia kìa, rõ là đã quá cũ kỹ rồi. Sao người ta không cho nó "nghỉ hưu" nhỉ?</t>
         </is>
       </c>
     </row>
@@ -24884,7 +24884,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Nhìn những ngọn núi tuyết kia thôi mà ta đã muốn lao thẳng tới rồi.</t>
+          <t>Nhìn những ngọn núi tuyết kia thôi mà tao đã muốn lao thẳng tới rồi.</t>
         </is>
       </c>
     </row>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Ta nhớ địa chỉ WavesLine của ngươi ở vùng băng giá. Giờ ngươi đã đến đây rồi, không muốn ở lại thêm chút à?</t>
+          <t>Tao nhớ địa chỉ WavesLine của mày ở vùng băng giá. Giờ mày đã đến đây rồi, không muốn ở lại thêm chút à?</t>
         </is>
       </c>
     </row>
@@ -25079,7 +25079,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>...Ta viết thế chủ yếu để tạo không khí thôi.</t>
+          <t>...Tao viết thế chủ yếu để tạo không khí thôi.</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Bạn đang nhìn gì vậy?</t>
+          <t>Nhìn gì thế?</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Ta sẽ đến giúp một tay. Còn ngươi thì đăng bài kêu gọi trợ giúp lên Diễn Đàn Học Viện đi...</t>
+          <t>Tao sẽ đến giúp một tay. Còn mày thì đăng bài kêu gọi trợ giúp lên Diễn Đàn Học Viện đi...</t>
         </is>
       </c>
     </row>
@@ -27679,7 +27679,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>...Đúng thế. Ta đã mơ về khoảnh khắc này biết bao lần. Được tận mắt chứng kiến thực thể khổng lồ, bí ẩn và mạnh mẽ đến không tưởng ấy...</t>
+          <t>...Đúng thế. Tao đã mơ về khoảnh khắc này biết bao lần. Được tận mắt chứng kiến thực thể khổng lồ, bí ẩn và mạnh mẽ đến không tưởng ấy...</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Ta thấy... nhẹ bẫng. Chóng mặt. Thậm chí còn hơi... sợ nữa?</t>
+          <t>Tao thấy... nhẹ bẫng. Chóng mặt. Thậm chí còn hơi... sợ nữa?</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Dù ta không thể giúp "đỗ kỳ thi" được, nhưng với những điều đó, ta gửi thêm mấy quyển bài tập cho bọn trẻ...</t>
+          <t>Dù tao không thể giúp "đỗ kỳ thi" được, nhưng với những điều đó, tao gửi thêm mấy quyển bài tập cho bọn trẻ...</t>
         </is>
       </c>
     </row>
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Ta sẽ đến giúp một tay. Còn ngươi thì đăng bài kêu gọi trợ giúp lên Diễn Đàn Học Viện đi...</t>
+          <t>Tao sẽ đến giúp một tay. Còn mày thì đăng bài kêu gọi trợ giúp lên Diễn Đàn Học Viện đi...</t>
         </is>
       </c>
     </row>
@@ -31644,7 +31644,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Hắn khiến ta thấy hứng khởi...</t>
+          <t>Hắn khiến tao thấy hứng khởi...</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Nó đang liếm ta… Cứuuuuuuuuu!</t>
+          <t>Nó đang liếm tao… Cứuuuuuuuuu!</t>
         </is>
       </c>
     </row>
@@ -31904,7 +31904,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Đứng yên nào! Ta phải quay clip này...</t>
+          <t>Đứng yên nào! Tao phải quay clip này...</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Ta sẽ làm! Khi nào sửa xong, chúng mình phải đi thử ngay!</t>
+          <t>Tao sẽ làm! Khi nào sửa xong, chúng mình phải đi thử ngay!</t>
         </is>
       </c>
     </row>
